--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484773_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484773_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8429</v>
+        <v>3.4011</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0785</v>
+        <v>3.06</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7644</v>
+        <v>0.3412</v>
       </c>
       <c r="G2" t="n">
         <v>3.2298</v>
@@ -610,13 +610,13 @@
         <v>2.6418</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0089</v>
+        <v>-0.4329</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7613</v>
+        <v>-0.7798</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7702</v>
+        <v>0.3469</v>
       </c>
       <c r="V2" t="n">
         <v>-1.8488</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1667</v>
+        <v>2.3809</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9035</v>
+        <v>2.1442</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2632</v>
+        <v>0.2367</v>
       </c>
       <c r="G3" t="n">
         <v>1.1895</v>
@@ -688,13 +688,13 @@
         <v>3.0192</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3133</v>
+        <v>-0.4725</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2438</v>
+        <v>-0.5155</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.043</v>
       </c>
       <c r="V3" t="n">
         <v>1.6639</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7536</v>
+        <v>1.526</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9683</v>
+        <v>0.7935</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7854</v>
+        <v>0.7325</v>
       </c>
       <c r="G4" t="n">
         <v>1.4867</v>
@@ -766,13 +766,13 @@
         <v>0.5661</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1875</v>
+        <v>-0.0401</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1205</v>
+        <v>-0.0543</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0142</v>
       </c>
       <c r="V4" t="n">
         <v>-0.4867</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1901</v>
+        <v>0.8536</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2293</v>
+        <v>2.8928</v>
       </c>
       <c r="F5" t="n">
         <v>-2.0392</v>
@@ -844,10 +844,10 @@
         <v>1.6983</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8629</v>
+        <v>-0.1994</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0582</v>
+        <v>-0.3946</v>
       </c>
       <c r="U5" t="n">
         <v>0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4796</v>
+        <v>0.2839</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9715</v>
+        <v>1.5763</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4511</v>
+        <v>-1.2924</v>
       </c>
       <c r="G6" t="n">
         <v>0.6852</v>
@@ -922,13 +922,13 @@
         <v>3.0192</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9234</v>
+        <v>-1.16</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.7048</v>
+        <v>-1.1001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2186</v>
+        <v>-0.0599</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1849</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5389</v>
+        <v>-0.7241</v>
       </c>
       <c r="E7" t="n">
         <v>-0.7592</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2203</v>
+        <v>0.0351</v>
       </c>
       <c r="G7" t="n">
         <v>0.1456</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0429</v>
+        <v>-0.2281</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0747</v>
+        <v>-0.1105</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6415999999999999</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. FONT FENOLLAR</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4328</v>
+        <v>-1.319</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7671</v>
+        <v>-1.3394</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6656</v>
+        <v>0.0204</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5918</v>
+        <v>-1.1535</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9422</v>
+        <v>-0.1143</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6496</v>
+        <v>-1.0393</v>
       </c>
       <c r="J8" t="n">
         <v>-1.2991</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6496</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6496</v>
+        <v>-1.2991</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2927</v>
+        <v>0.1456</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2927</v>
+        <v>-0.1143</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2598</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,28 +1078,28 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4609</v>
+        <v>-0.1655</v>
       </c>
       <c r="T8" t="n">
-        <v>0.532</v>
+        <v>-0.0403</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0711</v>
+        <v>-0.1252</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.461</v>
+        <v>-1.5297</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5343</v>
+        <v>-0.294</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0733</v>
+        <v>-1.2358</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1535</v>
+        <v>1.8343</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1143</v>
+        <v>1.0268</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0393</v>
+        <v>0.8076</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2991</v>
+        <v>2.0515</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.3523</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2991</v>
+        <v>0.6992</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1456</v>
+        <v>-0.2172</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1143</v>
+        <v>-0.3256</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2598</v>
+        <v>0.1083</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3074</v>
+        <v>-0.1036</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2352</v>
+        <v>-0.1377</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0723</v>
+        <v>0.0341</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.7509</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.4301</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7918</v>
+        <v>-1.5952</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4502</v>
+        <v>-1.6051</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3416</v>
+        <v>0.01</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8343</v>
+        <v>-0.5939</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0268</v>
+        <v>0.0251</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8076</v>
+        <v>-0.6189</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0515</v>
+        <v>1.5099</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3523</v>
+        <v>2.5622</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6992</v>
+        <v>-1.0523</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2172</v>
+        <v>-2.1038</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3256</v>
+        <v>-2.5371</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1083</v>
+        <v>0.4334</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5096</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.887</v>
+        <v>-4.9062</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3774</v>
+        <v>2.6418</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3656</v>
+        <v>-1.2273</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2939</v>
+        <v>-1.001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0717</v>
+        <v>-0.2262</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7509</v>
+        <v>2.4904</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3208</v>
+        <v>2.7922</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4301</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>G. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1902</v>
+        <v>-1.7251</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.015</v>
+        <v>-1.0594</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1752</v>
+        <v>-0.6656</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5939</v>
+        <v>-1.5918</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0251</v>
+        <v>-0.9422</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6189</v>
+        <v>-0.6496</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5099</v>
+        <v>-1.2991</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5622</v>
+        <v>-0.6496</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0523</v>
+        <v>-0.6496</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1038</v>
+        <v>-0.2927</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.5371</v>
+        <v>-0.2927</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4334</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2644</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.9062</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6418</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8223</v>
+        <v>0.1686</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4109</v>
+        <v>0.2397</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4114</v>
+        <v>-0.0711</v>
       </c>
       <c r="V11" t="n">
-        <v>2.4904</v>
+        <v>-0.3018</v>
       </c>
       <c r="W11" t="n">
-        <v>2.7922</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>-0.3018</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8218</v>
+        <v>-2.4334</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9419</v>
+        <v>-1.8445</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8799</v>
+        <v>-0.5889</v>
       </c>
       <c r="G12" t="n">
         <v>0.3684</v>
@@ -1390,13 +1390,13 @@
         <v>1.1322</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.492</v>
+        <v>-1.1035</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.823</v>
+        <v>-0.7256</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.3779</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7628</v>
+        <v>-0.881</v>
       </c>
       <c r="E13" t="n">
-        <v>2.683400000000001</v>
+        <v>3.565199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.446</v>
+        <v>-4.446000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>8.139999999999999</v>
@@ -1438,7 +1438,7 @@
         <v>-1.3851</v>
       </c>
       <c r="I13" t="n">
-        <v>9.5252</v>
+        <v>9.525200000000002</v>
       </c>
       <c r="J13" t="n">
         <v>16.5535</v>
@@ -1447,7 +1447,7 @@
         <v>13.0926</v>
       </c>
       <c r="L13" t="n">
-        <v>3.460800000000001</v>
+        <v>3.4608</v>
       </c>
       <c r="M13" t="n">
         <v>-8.413399999999999</v>
@@ -1468,13 +1468,13 @@
         <v>15.096</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.8459</v>
+        <v>-4.964300000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.508599999999999</v>
+        <v>-4.6268</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3372999999999999</v>
+        <v>-0.3374000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1697</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.4954</v>
+        <v>8.513400000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>6.8838</v>
+        <v>6.9812</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6116</v>
+        <v>1.5323</v>
       </c>
       <c r="G14" t="n">
         <v>4.4032</v>
@@ -1546,13 +1546,13 @@
         <v>1.887</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6772</v>
+        <v>0.6953</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1147</v>
+        <v>-0.0172</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7919</v>
+        <v>0.7125</v>
       </c>
       <c r="V14" t="n">
         <v>2.4714</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5919</v>
+        <v>5.2304</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5228</v>
+        <v>4.7433</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0691</v>
+        <v>0.4871</v>
       </c>
       <c r="G15" t="n">
         <v>1.4394</v>
@@ -1624,13 +1624,13 @@
         <v>1.5096</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6994</v>
+        <v>1.338</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0669</v>
+        <v>0.2874</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6326</v>
+        <v>1.0506</v>
       </c>
       <c r="V15" t="n">
         <v>0.9434</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5346</v>
+        <v>1.7022</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1036</v>
+        <v>1.3242</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4309</v>
+        <v>0.378</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1525</v>
@@ -1702,13 +1702,13 @@
         <v>1.6983</v>
       </c>
       <c r="S16" t="n">
-        <v>1.536</v>
+        <v>0.7036</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1844</v>
+        <v>0.405</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3516</v>
+        <v>0.2987</v>
       </c>
       <c r="V16" t="n">
         <v>1.585</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3779</v>
+        <v>1.4224</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5735</v>
+        <v>1.6709</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1956</v>
+        <v>-0.2485</v>
       </c>
       <c r="G17" t="n">
         <v>0.3812</v>
@@ -1780,13 +1780,13 @@
         <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1288</v>
+        <v>0.1733</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.5492</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7754</v>
+        <v>0.7225</v>
       </c>
       <c r="V17" t="n">
         <v>0.3018</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1232</v>
+        <v>1.2904</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8014</v>
+        <v>0.704</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3219</v>
+        <v>0.5864</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0924</v>
@@ -1858,13 +1858,13 @@
         <v>1.3209</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1052</v>
+        <v>0.0619</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1147</v>
+        <v>-0.2121</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0094</v>
+        <v>0.274</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2916</v>
+        <v>-0.1677</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.0221</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2163</v>
+        <v>-0.1898</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2504</v>
@@ -1936,13 +1936,13 @@
         <v>0.1887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2299</v>
+        <v>-0.106</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1176</v>
+        <v>-0.0201</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2085</v>
+        <v>-0.8897</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7085</v>
+        <v>-0.4162</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5</v>
+        <v>-0.4735</v>
       </c>
       <c r="G20" t="n">
         <v>1.3573</v>
@@ -2014,13 +2014,13 @@
         <v>1.5096</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4908</v>
+        <v>0.8096</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1234</v>
+        <v>0.4157</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3675</v>
+        <v>0.3939</v>
       </c>
       <c r="V20" t="n">
         <v>-1.547</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1955</v>
+        <v>-1.8503</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5675</v>
+        <v>-1.2752</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.628</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7587</v>
@@ -2092,13 +2092,13 @@
         <v>2.0757</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1534</v>
+        <v>0.1918</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7642</v>
+        <v>-0.4719</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6108</v>
+        <v>0.6637</v>
       </c>
       <c r="V21" t="n">
         <v>0.6036</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9182</v>
+        <v>-3.1833</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1056</v>
+        <v>-2.4236</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8126</v>
+        <v>-0.7597</v>
       </c>
       <c r="G22" t="n">
         <v>-4.7307</v>
@@ -2170,13 +2170,13 @@
         <v>2.0757</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0012</v>
+        <v>0.7361</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7026</v>
+        <v>-0.0205</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7037</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0.6226</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3753</v>
+        <v>-4.2959</v>
       </c>
       <c r="E23" t="n">
         <v>-3.8632</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5121</v>
+        <v>-0.4327</v>
       </c>
       <c r="G23" t="n">
         <v>-5.6955</v>
@@ -2248,13 +2248,13 @@
         <v>2.0757</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9993</v>
+        <v>1.0787</v>
       </c>
       <c r="T23" t="n">
         <v>0.5966</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4027</v>
+        <v>0.4821</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6226</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3712</v>
+        <v>-6.0092</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1189</v>
+        <v>-3.0215</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2522</v>
+        <v>-2.9877</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0409</v>
@@ -2326,13 +2326,13 @@
         <v>1.1322</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1981</v>
+        <v>0.1638</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1735</v>
+        <v>-0.076</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0247</v>
+        <v>0.2399</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1886</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.762699999999997</v>
+        <v>1.762700000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>4.4461</v>
+        <v>4.446</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.6833</v>
+        <v>-2.683199999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-8.140000000000001</v>
@@ -2404,13 +2404,13 @@
         <v>16.983</v>
       </c>
       <c r="S25" t="n">
-        <v>5.846099999999999</v>
+        <v>5.8461</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3372999999999998</v>
+        <v>0.3377000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>5.508599999999999</v>
+        <v>5.508699999999999</v>
       </c>
       <c r="V25" t="n">
         <v>2.169600000000001</v>
